--- a/outputs/Заявка в Корею.xlsx
+++ b/outputs/Заявка в Корею.xlsx
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>100</v>
+        <v>624</v>
       </c>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>150</v>
+        <v>1355</v>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>100</v>
+        <v>759</v>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>100</v>
+        <v>614</v>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="3" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="3" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="3" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="3" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="3" t="n">
-        <v>100</v>
+        <v>428</v>
       </c>
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>100</v>
+        <v>405</v>
       </c>
       <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" s="3" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
@@ -4515,7 +4515,7 @@
       <c r="C104" s="4" t="inlineStr"/>
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="5" t="n">
-        <v>15500</v>
+        <v>21159</v>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
       <c r="G104" s="4" t="inlineStr"/>

--- a/outputs/Заявка в Корею.xlsx
+++ b/outputs/Заявка в Корею.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -453,10 +453,6 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="58" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,26 +496,6 @@
           <t>Комментарий поставщика</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Остаток, шт</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Товар</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Последняя известная цена, KRW</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Где видели</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -546,22 +522,6 @@
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для восстановления защитного барьера кожи лица</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>11931.81818181818</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -588,22 +548,6 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pads]/Тонер-пэды от воспалений</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>8509.090909090908</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -630,22 +574,6 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" s="3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/успокаивающие тонер-пэды</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>1526</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -672,22 +600,6 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выравнивания тона и рельефа кожи лица</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>9508</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -714,22 +626,6 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>1375</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тонер-пэды для выравнивания тона и рельефа кожи</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>7950</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -756,22 +652,6 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворотка для выравнивания тона и рельефа кожи лица</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>9900</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -798,22 +678,6 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восстанавливающая сыворотка с экстрактом нони для лица</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>11194</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -840,22 +704,6 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]/Восстанавливающий тонер с экстрактом нони</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>9886.363636363634</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -882,22 +730,6 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" s="3" t="n">
-        <v>9493</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/Подтягивающий бустер-крем с ретинолом для лица</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>9540</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -924,22 +756,6 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" s="3" t="n">
-        <v>3112</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыворотка с ретинолом и микроиглами для лица</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>9794</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -962,16 +778,6 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" s="3" t="n">
-        <v>4520</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Celimax Dual Barrier Creamy Toner, тонер 150 мл</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -994,16 +800,6 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml] / Бальзам от выпадения волос Чёрный чеснок</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1026,16 +822,6 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]/ Шампунь с черным чесноком против выпадения волос</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1058,16 +844,6 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шампунь с черным чесноком против выпадения волос</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1090,16 +866,6 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml] / Коллагеновая маска для волос</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1122,16 +888,6 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" s="3" t="n">
-        <v>7340</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняющий крем для лица с коллагеном</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1154,16 +910,6 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" s="3" t="n">
-        <v>344</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1176,26 +922,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8809605870962</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]/Консилер для лица (основная карточка)</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1208,26 +948,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8809605870979</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Консилер для лица (основная карточка)</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1240,26 +974,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8809605870986</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Консилер для лица (основаная карточка)</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1267,31 +995,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8809605877251</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" s="3" t="n">
-        <v>7279</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий скраб для лица с содой</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1299,41 +1021,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N10</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8809595053659</t>
+          <t>8809605877268</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" s="3" t="n">
-        <v>2435</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер с аргановым маслом</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>3730</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1341,41 +1047,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8809034583617</t>
+          <t>8809605877275</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" s="3" t="n">
-        <v>3239</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь-кондиционер 2в1 с экстрактом черного чеснока</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>3660</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1383,41 +1073,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8800260032009</t>
+          <t>8809605877282</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" s="3" t="n">
-        <v>6179</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml] / Сыворотка с коллагеном и гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>4660</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1425,17 +1099,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8809317289472</t>
+          <t>8809605877299</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1444,22 +1118,6 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для умывания</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1930</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1467,17 +1125,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N35</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8802221001338</t>
+          <t>8809605877305</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1486,22 +1144,6 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняющий крем с коллагеном</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>5790</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1509,17 +1151,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N40</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8809480772504</t>
+          <t>8809605877312</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -1528,22 +1170,6 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml] / Сыворотка роллер для глаз</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>2770</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1551,41 +1177,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
+          <t>ENOUGH Collagen 3X Moisture Stick Foundation #13N</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8809595053284</t>
+          <t>8809951050636</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" s="3" t="n">
-        <v>3493</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml] / Шампунь-кондиционер 2в1 с коллагеном</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>3660</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1593,17 +1203,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g]</t>
+          <t>ENOUGH Collagen 3X Moisture Stick Foundation #21N</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8809317289274</t>
+          <t>8809951050643</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -1612,22 +1222,6 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" s="3" t="n">
-        <v>860</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>4010</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1635,17 +1229,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>ENOUGH Collagen Moisture Foundation #13</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8809480770975</t>
+          <t>8809280062362</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -1654,22 +1248,6 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий крем с муцином улитки и коллоидным золотом</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>6390</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1677,17 +1255,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>ENOUGH Collagen Moisture Foundation #21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8809469772778</t>
+          <t>8809280062379</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
@@ -1696,22 +1274,6 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" s="3" t="n">
-        <v>901</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с улиткой</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>4660</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1719,17 +1281,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml]</t>
+          <t>ENOUGH Collagen Moisture Foundation #23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8809481760463</t>
+          <t>8809280062386</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
@@ -1738,22 +1300,6 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" s="3" t="n">
-        <v>941</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / База под макияж SPF50+ PA+++</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>8565</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1761,17 +1307,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8809541280269</t>
+          <t>8809474497062</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
@@ -1780,22 +1326,6 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml] / Ампульная маска с экстрактом алое</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1803,41 +1333,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #21</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8809210034087</t>
+          <t>8809474497079</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" s="3" t="n">
-        <v>1614</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной крем с экстрактом ласточкиного гнезда</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1845,17 +1359,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8809541280238</t>
+          <t>8809605870856</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
@@ -1864,22 +1378,6 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml] / Ампульная маска с экстрактом слизи черной улитки</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1887,41 +1385,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>8809541280245</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml] / Ампульная маска с экстрактом камелии</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1929,41 +1407,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>8809541280283</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml] / Ампульная маска с экстрактом икры</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1971,41 +1429,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>8809541280160</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml] / Ампульная маска с коллагеном</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2013,17 +1451,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8809541280146</t>
+          <t>8809605871938</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
@@ -2032,22 +1470,6 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml] / Тканевая маска с экстрактом огурца</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2055,17 +1477,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8809541282447</t>
+          <t>8809605871945</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
@@ -2074,22 +1496,6 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с центеллой азиатской</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2097,17 +1503,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #23</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8809541280177</t>
+          <t>8809605871952</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
@@ -2116,22 +1522,6 @@
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml] / Ампульная маска с экстрактом зеленого чая</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2139,17 +1529,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8809541280214</t>
+          <t>8809605870993</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
@@ -2158,22 +1548,6 @@
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml] / Ампульная маска с экстрактом меда</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2181,17 +1555,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #21</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8809541280207</t>
+          <t>8809605871006</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -2200,22 +1574,6 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml] / Ампульная маска с гиалуроновой кислотой</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2223,17 +1581,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #23</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8809541280184</t>
+          <t>8809605871013</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
@@ -2242,22 +1600,6 @@
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml] / Ампульная маска с экстрактом лотоса</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2265,17 +1607,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>ENOUGH gold snail moisture foundation #13</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8809541282508</t>
+          <t>8809474498809</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -2284,22 +1626,6 @@
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2307,17 +1633,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH gold snail moisture foundation #21</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8809541280221</t>
+          <t>8809474498816</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
@@ -2326,22 +1652,6 @@
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml] / ампульная маска для лица с жемчугом</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2349,41 +1659,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>8809541280191</t>
-        </is>
-      </c>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" s="3" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml] / Ампульная маска с плацентой</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2391,41 +1681,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8809541280153</t>
+          <t>8809595053659</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml] / Ампульная маска с экстрактом граната</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2433,41 +1707,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8809541280252</t>
+          <t>8809034583617</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml] / Ампульная маска с экстрактом картофеля</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2475,41 +1733,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8809541280276</t>
+          <t>8800260032009</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml] / Ампульная маска с красным женьшенем</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2517,41 +1759,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8809210034124</t>
+          <t>8809317289472</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" s="3" t="n">
-        <v>7463</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняющий антивозрастной</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2559,17 +1785,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8809210036517</t>
+          <t>8802221001338</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
@@ -2578,22 +1804,6 @@
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2601,17 +1811,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8809541282461</t>
+          <t>8809480772504</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
@@ -2620,22 +1830,6 @@
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с коллагеном антивозрастной</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>2160</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2643,41 +1837,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8809541280139</t>
+          <t>8809595053284</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" s="3" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml] / Ампульная маска с витаминами</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2685,31 +1863,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8809317289274</t>
+        </is>
+      </c>
       <c r="E56" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea] / Ультратонкая тканевая маска с ласточкиным гнездом</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2717,31 +1889,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8809480770975</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea] / Ультратонкая тканевая маска с золотом и икрой</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2749,31 +1915,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8809469772778</t>
+        </is>
+      </c>
       <c r="E58" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea] / Ультратонкая тканевая маска с экстрактом медузы</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2781,31 +1941,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - 10</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8809481760463</t>
+        </is>
+      </c>
       <c r="E59" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" s="3" t="n">
-        <v>832</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] - ассорти набор из 10шт</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2813,31 +1967,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8809541280269</t>
+        </is>
+      </c>
       <c r="E60" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea] / Тканевая маска для лица с экстрактом кордицепса и комплексом аминокислот</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2845,31 +1993,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8809210034087</t>
+        </is>
+      </c>
       <c r="E61" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea] / Ультраувлажняющая тканевая маска</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2877,17 +2019,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea]</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8809696353658</t>
+          <t>8809541280238</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
@@ -2896,22 +2038,6 @@
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea] / Ультратонкая тканевая маска с черной икрой</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>3740</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2919,17 +2045,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8809711711531</t>
+          <t>8809541280245</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
@@ -2938,22 +2064,6 @@
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>5511</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2961,17 +2071,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8809696354129</t>
+          <t>8809541280283</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
@@ -2980,22 +2090,6 @@
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea / Регенерирующая маска для лица с центеллой</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>3740</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3003,17 +2097,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JMSOLUTION JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea]</t>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8809794737022</t>
+          <t>8809541280160</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
@@ -3022,22 +2116,6 @@
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>JMSOLUTION  JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea] / Тканевая маска</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>5511</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3045,17 +2123,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8809711712491</t>
+          <t>8809541280146</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
@@ -3064,22 +2142,6 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>5511</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3087,17 +2149,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8809445616553</t>
+          <t>8809541282447</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
@@ -3106,22 +2168,6 @@
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" s="3" t="n">
-        <v>400</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для глаз антивозрастной с пептидами</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>1350</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3129,41 +2175,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml]</t>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8809730952236</t>
+          <t>8809541280177</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>624</v>
+        <v>100</v>
       </c>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" s="3" t="n">
-        <v>624</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий лосьон с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>9750</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3171,41 +2201,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml]</t>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8809657114687</t>
+          <t>8809541280214</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1355</v>
+        <v>100</v>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" s="3" t="n">
-        <v>1355</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная сыворотка для лица</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>8970</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3213,41 +2227,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml]</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8809730952014</t>
+          <t>8809541280207</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>759</v>
+        <v>100</v>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" s="3" t="n">
-        <v>759</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыворотка с Витамином C</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>9750</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3255,31 +2253,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml]</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>8809541280184</t>
+        </is>
+      </c>
       <c r="E71" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для глубокого очищения</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3287,41 +2279,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8809567929722</t>
+          <t>8809541282508</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>650</v>
+        <v>100</v>
       </c>
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" s="3" t="n">
-        <v>650</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для умывания с бифидобактериями</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>8970</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3329,41 +2305,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8809730957705</t>
+          <t>8809541280221</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>614</v>
+        <v>100</v>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" s="3" t="n">
-        <v>614</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с микроиглами и пробиотиками</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>15210</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3371,31 +2331,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>8809541280191</t>
+        </is>
+      </c>
       <c r="E74" s="3" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлаждающие гидрогелевые патчи для глаз с экстрактом агавы</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3403,41 +2357,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8809508850450</t>
+          <t>8809541280153</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлаждающая гидрогелевая маска для лица с экстрактом агавы</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>7390</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3445,31 +2383,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>8809541280252</t>
+        </is>
+      </c>
       <c r="E76" s="3" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / Смягчающие гидрогелевые патчи для глаз с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3477,41 +2409,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8809508850566</t>
+          <t>8809541280276</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / Смягчающая гидрогелевая маска для лица с экстрактом артишока</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>7390</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3519,31 +2435,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8809210034124</t>
+        </is>
+      </c>
       <c r="E78" s="3" t="n">
-        <v>89</v>
+        <v>750</v>
       </c>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3551,31 +2461,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>8809210036517</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3583,31 +2487,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8809541282461</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]/ Гидрогелевые патчи для глаз с черным жемчугом и золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3615,41 +2513,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8809239801820</t>
+          <t>8809541280139</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>216</v>
+        <v>100</v>
       </c>
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с черным жемчугом и золотом</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>5860</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3657,41 +2539,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>8809508850191</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с черным жемчугом и золотом</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>7100</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3699,31 +2561,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="3" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3731,31 +2583,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тонизирующая гидрогелевая маска для лица с экстрактом какао</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3763,31 +2605,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8809794737022</t>
+        </is>
+      </c>
       <c r="E85" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / Успокаивающие гидрогелевые патчи для глаз с экстрактом ромашки</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3795,41 +2631,21 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>8809239800458</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] 10</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" s="3" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" s="3" t="n">
-        <v>360</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с коллагеном и коэнзимом Q10</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>5860</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3837,41 +2653,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>8809239800618</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидрогелевые патчи с золотом и EGF</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>5860</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3879,41 +2675,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>8809239802872</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" s="3" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогелевые патчи для глаз с золотом и улиткой</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>6330</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3921,41 +2697,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8809239802896</t>
+          <t>8809696353658</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом и экстрактом улитки</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>7100</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3963,31 +2723,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>8809711711531</t>
+        </is>
+      </c>
       <c r="E90" s="3" t="n">
-        <v>428</v>
+        <v>100</v>
       </c>
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs] / гидрогелевые патчи для глаз с золотом 1 пара</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3995,41 +2749,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea]</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8809239803596</t>
+          <t>8809696354129</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>405</v>
+        <v>100</v>
       </c>
       <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" s="3" t="n">
-        <v>405</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>6330</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4037,41 +2775,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8809239803589</t>
+          <t>8809711712491</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая маска для лица с золотом</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>7100</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4079,31 +2801,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>8809445616553</t>
+        </is>
+      </c>
       <c r="E93" s="3" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые патчи для век увлажняющие</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4111,41 +2827,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8809738608364</t>
+          <t>8809730952236</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>700</v>
+        <v>624</v>
       </c>
       <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" s="3" t="n">
-        <v>7126</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для умывания лица</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>5857</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4153,41 +2853,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>8809657114731</t>
+          <t>8809657114687</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>100</v>
+        <v>1355</v>
       </c>
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" s="3" t="n">
-        <v>966</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с морской водой</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>7100</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4195,41 +2879,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8809738600221</t>
+          <t>8809730952014</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>100</v>
+        <v>759</v>
       </c>
       <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий крем с березовым соком</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>11702</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4237,41 +2905,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>8809738593080</t>
-        </is>
-      </c>
+          <t>MANYO - Pure Cleansing Oil [200ml]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" s="3" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" s="3" t="n">
-        <v>1422</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка для умывания лица от прыщей и акне</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>5963</v>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4279,41 +2927,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8809783325667</t>
+          <t>8809567929722</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жирной кожи лица увлажняющая с центеллой</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="n">
-        <v>8293</v>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>G&amp;E Global</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4321,41 +2953,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8809738604755</t>
+          <t>8809730957705</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>100</v>
+        <v>614</v>
       </c>
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка для лица успокаивающая из экстракта центеллы.</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>4922.727272727273</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Papa Cosmetic</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4363,41 +2979,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>8809326334224</t>
-        </is>
-      </c>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" s="3" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g] / Крем для лица</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="n">
-        <v>11988</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Классик</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4405,31 +3001,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>THE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml]</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8809508850450</t>
+        </is>
+      </c>
       <c r="E101" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml] / Тоник с гликолевой кислотой 7%</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4437,31 +3027,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" s="3" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4469,63 +3049,677 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>8809695678363</t>
+          <t>8809508850566</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" s="3" t="n">
-        <v>397</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>VT REEDLE SHOT 100 / Бустер-сыворотка с микроиглами</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="n">
-        <v>14559.6</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>GlowBeauty</t>
-        </is>
-      </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr"/>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>8809239801820</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>8809508850191</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>8809239800458</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye Spot Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>8809239800618</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>8809239802872</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>8809239802896</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>8809239803589</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>8809738608364</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>8809657114731</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>8809738600221</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>8809738593080</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>8809783325667</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>8809738604755</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>8809326334224</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>THE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml]</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>8809695678363</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr"/>
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="5" t="n">
-        <v>21159</v>
-      </c>
-      <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr"/>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="5" t="n">
-        <v>110205</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr"/>
-      <c r="K104" s="5" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
+      <c r="C130" s="4" t="inlineStr"/>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>23759</v>
+      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Заявка в Корею.xlsx
+++ b/outputs/Заявка в Корею.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml]</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="3" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g]</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -922,14 +922,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #13</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8809605870962</t>
-        </is>
-      </c>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" s="3" t="n">
         <v>100</v>
       </c>
@@ -948,16 +944,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #21</t>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8809605870979</t>
+          <t>8809605870962</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -974,16 +970,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #23</t>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8809605870986</t>
+          <t>8809605870979</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
@@ -1000,12 +996,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N00</t>
+          <t>ENOUGH 8 Peptide Full Cover Perfect Foundation #23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8809605877251</t>
+          <t>8809605870986</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
@@ -1026,16 +1022,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N10</t>
+          <t>ENOUGH Collagen 3X Moisture Ampoule</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8809605877268</t>
+          <t>8809541378546</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1052,16 +1048,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N20</t>
+          <t>ENOUGH Collagen 3X Moisture Cream</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8809605877275</t>
+          <t>8809755465285</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1078,12 +1074,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N25</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8809605877282</t>
+          <t>8809605877251</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -1104,12 +1100,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N30</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8809605877299</t>
+          <t>8809605877268</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1130,12 +1126,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N35</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8809605877305</t>
+          <t>8809605877275</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1156,12 +1152,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N40</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8809605877312</t>
+          <t>8809605877282</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
@@ -1182,12 +1178,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Stick Foundation #13N</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8809951050636</t>
+          <t>8809605877299</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -1208,12 +1204,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen 3X Moisture Stick Foundation #21N</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N35</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8809951050643</t>
+          <t>8809605877305</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
@@ -1234,12 +1230,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Moisture Foundation #13</t>
+          <t>ENOUGH Collagen 3X Moisture Foundation SPF 15 #N40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8809280062362</t>
+          <t>8809605877312</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
@@ -1260,16 +1256,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Moisture Foundation #21</t>
+          <t>ENOUGH Collagen 3X Moisture Makeup Fixer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8809280062379</t>
+          <t>8809438489584</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1286,16 +1282,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Moisture Foundation #23</t>
+          <t>ENOUGH Collagen 3X Moisture Mist</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8809280062386</t>
+          <t>8809438489577</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1312,12 +1308,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Whitening Moisture Foundation #13</t>
+          <t>ENOUGH Collagen 3X Moisture Stick Foundation #13N</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8809474497062</t>
+          <t>8809951050636</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
@@ -1338,12 +1334,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Whitening Moisture Foundation #21</t>
+          <t>ENOUGH Collagen 3X Moisture Stick Foundation #21N</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8809474497079</t>
+          <t>8809951050643</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
@@ -1364,16 +1360,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen Whitening Moisture Foundation #23</t>
+          <t>ENOUGH Collagen 3X Moisture Sun Cream SPF50+ PA++++</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8809605870856</t>
+          <t>8809975191131</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1390,12 +1386,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>ENOUGH Collagen Hydro Moisture Two Way Cake #13</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8809347960303</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1412,12 +1412,16 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>ENOUGH Collagen Hydro Moisture Two Way Cake #21</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8809347960310</t>
+        </is>
+      </c>
       <c r="E38" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1434,12 +1438,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>ENOUGH Collagen Moisture Foundation #13</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8809280062362</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1456,16 +1464,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #13</t>
+          <t>ENOUGH Collagen Moisture Foundation #21</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8809605871938</t>
+          <t>8809280062379</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
@@ -1482,16 +1490,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #21</t>
+          <t>ENOUGH Collagen Moisture Foundation #23</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8809605871945</t>
+          <t>8809280062386</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
@@ -1508,16 +1516,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #23</t>
+          <t>ENOUGH Collagen Moisture Sun Cream</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8809605871952</t>
+          <t>8809755462123</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1534,16 +1542,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #13</t>
+          <t>ENOUGH Collagen Whitening Moisture Cream</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8809605870993</t>
+          <t>8809480652165</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1560,16 +1568,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #21</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #13</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8809605871006</t>
+          <t>8809474497062</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1586,16 +1594,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #23</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #21</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8809605871013</t>
+          <t>8809474497079</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1612,12 +1620,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENOUGH gold snail moisture foundation #13</t>
+          <t>ENOUGH Collagen Whitening Moisture Foundation #23</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8809474498809</t>
+          <t>8809605870856</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -1638,16 +1646,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENOUGH gold snail moisture foundation #21</t>
+          <t>ENOUGH Collagen Whitening Two way Cake #13</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8809474498816</t>
+          <t>8809480652097</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1659,17 +1667,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>ENOUGH Collagen Whitening Two way Cake #21</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8809480652103</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="n">
-        <v>750</v>
+        <v>20</v>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1681,21 +1693,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>8809595053659</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="3" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -1707,21 +1715,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>8809034583617</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" s="3" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1733,21 +1737,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>8800260032009</t>
-        </is>
-      </c>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
@@ -1759,21 +1759,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #13</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8809317289472</t>
+          <t>8809605871938</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
@@ -1785,21 +1785,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8802221001338</t>
+          <t>8809605871945</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
+          <t>ENOUGH Rich Gold Double Wear Radiance Foundation #23</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8809480772504</t>
+          <t>8809605871952</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
@@ -1837,21 +1837,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #13</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8809595053284</t>
+          <t>8809605870993</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
@@ -1863,21 +1863,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #21</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8809317289274</t>
+          <t>8809605871006</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
@@ -1889,17 +1889,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>ENOUGH Ultra X10 Cover up Collagen Foundation #23</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8809480770975</t>
+          <t>8809605871013</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -1915,21 +1915,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>ENOUGH Ultra X10 Sun Cream</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8809469772778</t>
+          <t>8809726960399</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -1941,21 +1941,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml]</t>
+          <t>ENOUGH gold snail moisture foundation #13</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8809481760463</t>
+          <t>8809474498809</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -1967,21 +1967,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JIGOTT - Aloe Real Ampoule Mask [27ml]</t>
+          <t>ENOUGH gold snail moisture foundation #21</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8809541280269</t>
+          <t>8809474498816</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -1993,21 +1993,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>8809210034087</t>
-        </is>
-      </c>
+          <t>Enough 8 Peptide Sensation Pro Balancing Cream</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" s="3" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -2019,21 +2015,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>8809541280238</t>
-        </is>
-      </c>
+          <t>Enough 8 Peptide Sensation Pro Sun Cream</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -2045,21 +2037,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JIGOTT - Camellia Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>8809541280245</t>
-        </is>
-      </c>
+          <t>Enough Collagen Moisture Essential Cream</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2071,21 +2059,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JIGOTT - Caviar Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>8809541280283</t>
-        </is>
-      </c>
+          <t>Enough Rich Gold Intensive Pro Nourishing Cream</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2097,21 +2081,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>8809541280160</t>
-        </is>
-      </c>
+          <t>Enough Ultra X10 Collagen Pro Marine Cream</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -2123,19 +2103,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml]</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>8809541280146</t>
-        </is>
-      </c>
+          <t>Enough gold snail moisture foundation 23</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="3" t="n">
         <v>100</v>
       </c>
@@ -2149,21 +2125,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>8809541282447</t>
-        </is>
-      </c>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" s="3" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -2175,21 +2147,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8809541280177</t>
+          <t>8809595053659</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -2201,21 +2173,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JIGOTT - Honey Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8809541280214</t>
+          <t>8809034583617</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -2227,21 +2199,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [250ml]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8809541280207</t>
+          <t>8800260032009</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
@@ -2253,17 +2225,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JIGOTT - Lotus Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8809541280184</t>
+          <t>8809317289472</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
@@ -2279,17 +2251,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8809541282508</t>
+          <t>8802221001338</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
@@ -2305,17 +2277,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JIGOTT - Pearl Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml]</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8809541280221</t>
+          <t>8809480772504</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
@@ -2331,21 +2303,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JIGOTT - Placenta Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8809541280191</t>
+          <t>8809595053284</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2357,17 +2329,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g]</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8809541280153</t>
+          <t>8809317289274</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
@@ -2383,17 +2355,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JIGOTT - Potato Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>8809541280252</t>
+          <t>8809480770975</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
@@ -2409,17 +2381,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml]</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8809541280276</t>
+          <t>8809469772778</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
@@ -2435,21 +2407,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8809210034124</t>
+          <t>8809481760463</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
@@ -2466,12 +2438,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>JIGOTT - Aloe Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8809210036517</t>
+          <t>8809541280269</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
@@ -2492,16 +2464,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8809541282461</t>
+          <t>8809210034087</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -2518,12 +2490,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml]</t>
+          <t>JIGOTT - Black Snail Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8809541280139</t>
+          <t>8809541280238</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
@@ -2539,15 +2511,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>JIGOTT - Camellia Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>8809541280245</t>
+        </is>
+      </c>
       <c r="E82" s="3" t="n">
         <v>100</v>
       </c>
@@ -2561,15 +2537,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>JIGOTT - Caviar Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>8809541280283</t>
+        </is>
+      </c>
       <c r="E83" s="3" t="n">
         <v>100</v>
       </c>
@@ -2583,15 +2563,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>JIGOTT - Collagen Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>8809541280160</t>
+        </is>
+      </c>
       <c r="E84" s="3" t="n">
         <v>100</v>
       </c>
@@ -2605,17 +2589,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea]</t>
+          <t>JIGOTT - Cucumber Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>8809794737022</t>
+          <t>8809541280146</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
@@ -2631,15 +2615,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] 10</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8809541282447</t>
+        </is>
+      </c>
       <c r="E86" s="3" t="n">
         <v>100</v>
       </c>
@@ -2653,15 +2641,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>JIGOTT - Green Tea Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8809541280177</t>
+        </is>
+      </c>
       <c r="E87" s="3" t="n">
         <v>100</v>
       </c>
@@ -2675,15 +2667,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea]</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>JIGOTT - Honey Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>8809541280214</t>
+        </is>
+      </c>
       <c r="E88" s="3" t="n">
         <v>100</v>
       </c>
@@ -2697,17 +2693,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea]</t>
+          <t>JIGOTT - Hyaluronic Acid Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8809696353658</t>
+          <t>8809541280207</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
@@ -2723,17 +2719,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>JIGOTT - Lotus Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8809711711531</t>
+          <t>8809541280184</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
@@ -2749,17 +2745,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8809696354129</t>
+          <t>8809541282508</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
@@ -2775,17 +2771,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JIGOTT - Pearl Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8809711712491</t>
+          <t>8809541280221</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
@@ -2801,17 +2797,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>JIGOTT - Placenta Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>8809445616553</t>
+          <t>8809541280191</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
@@ -2827,21 +2823,21 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml]</t>
+          <t>JIGOTT - Pomegranate Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8809730952236</t>
+          <t>8809541280153</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>624</v>
+        <v>100</v>
       </c>
       <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
@@ -2853,21 +2849,21 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml]</t>
+          <t>JIGOTT - Potato Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>8809657114687</t>
+          <t>8809541280252</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>1355</v>
+        <v>100</v>
       </c>
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
@@ -2879,21 +2875,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml]</t>
+          <t>JIGOTT - Red Ginseng Real Ampoule Mask [27ml]</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8809730952014</t>
+          <t>8809541280276</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>759</v>
+        <v>100</v>
       </c>
       <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
@@ -2905,17 +2901,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml]</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>8809210034124</t>
+        </is>
+      </c>
       <c r="E97" s="3" t="n">
-        <v>80</v>
+        <v>750</v>
       </c>
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -2927,21 +2927,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8809567929722</t>
+          <t>8809210036517</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>650</v>
+        <v>100</v>
       </c>
       <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
@@ -2953,21 +2953,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8809730957705</t>
+          <t>8809541282461</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>614</v>
+        <v>100</v>
       </c>
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
@@ -2979,17 +2979,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>JIGOTT - Vitamin Real Ampoule Mask [27ml]</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>8809541280139</t>
+        </is>
+      </c>
       <c r="E100" s="3" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
@@ -3001,21 +3005,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>8809508850450</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
@@ -3027,17 +3027,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
+          <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" s="3" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
@@ -3049,21 +3049,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>8809508850566</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
@@ -3075,17 +3071,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>JMSOLUTION - Glory Aqua TOCOPHEROL VITAMIN C MASK PLUS [30ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>8809794737022</t>
+        </is>
+      </c>
       <c r="E104" s="3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
@@ -3097,17 +3097,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
+          <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] 10</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" s="3" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
@@ -3119,17 +3119,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
+          <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea]</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" s="3" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="F106" s="3" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
@@ -3141,21 +3141,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>8809239801820</t>
-        </is>
-      </c>
+          <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea]</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" s="3" t="n">
-        <v>216</v>
+        <v>100</v>
       </c>
       <c r="F107" s="3" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
@@ -3167,21 +3163,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK [30ml*10ea]</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>8809508850191</t>
+          <t>8809696353658</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F108" s="3" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
@@ -3193,17 +3189,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>8809711711531</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="F109" s="3" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
@@ -3215,17 +3215,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>8809696354129</t>
+        </is>
+      </c>
       <c r="E110" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
@@ -3237,17 +3241,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>8809711712491</t>
+        </is>
+      </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F111" s="3" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
@@ -3259,21 +3267,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea]</t>
+          <t>Lip Sleeping Mask EX berry</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>8809239800458</t>
+          <t>8809685797173</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="F112" s="3" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
@@ -3285,21 +3293,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye Spot Patch [60ea]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>8809239800618</t>
+          <t>8809445616553</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F113" s="3" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
@@ -3311,21 +3319,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea]</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml]</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>8809239802872</t>
+          <t>8809730952236</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>144</v>
+        <v>624</v>
       </c>
       <c r="F114" s="3" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -3337,21 +3345,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml]</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>8809239802896</t>
+          <t>8809657114687</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>150</v>
+        <v>1355</v>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -3363,17 +3371,21 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>MANYO - Galac Whitening Vita Serum [50ml]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>8809730952014</t>
+        </is>
+      </c>
       <c r="E116" s="3" t="n">
-        <v>428</v>
+        <v>759</v>
       </c>
       <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
@@ -3385,21 +3397,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>8809239803596</t>
-        </is>
-      </c>
+          <t>MANYO - Pure Cleansing Oil [200ml]</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" s="3" t="n">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="F117" s="3" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -3411,21 +3419,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>8809239803589</t>
+          <t>8809567929722</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>390</v>
+        <v>650</v>
       </c>
       <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
@@ -3437,17 +3445,21 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>8809730957705</t>
+        </is>
+      </c>
       <c r="E119" s="3" t="n">
-        <v>117</v>
+        <v>614</v>
       </c>
       <c r="F119" s="3" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -3459,21 +3471,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>8809738608364</t>
-        </is>
-      </c>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" s="3" t="n">
-        <v>700</v>
+        <v>360</v>
       </c>
       <c r="F120" s="3" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -3485,21 +3493,21 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>8809657114731</t>
+          <t>8809508850450</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F121" s="3" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
@@ -3511,21 +3519,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>8809738600221</t>
-        </is>
-      </c>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" s="3" t="n">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="F122" s="3" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
@@ -3537,21 +3541,21 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>8809738593080</t>
+          <t>8809508850566</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F123" s="3" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
@@ -3563,21 +3567,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>8809783325667</t>
-        </is>
-      </c>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" s="3" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
@@ -3589,21 +3589,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>8809738604755</t>
-        </is>
-      </c>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" s="3" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
@@ -3615,21 +3611,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>8809326334224</t>
-        </is>
-      </c>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" s="3" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="F126" s="3" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
@@ -3641,17 +3633,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>THE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml]</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>8809239801820</t>
+        </is>
+      </c>
       <c r="E127" s="3" t="n">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
@@ -3663,17 +3659,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>8809508850191</t>
+        </is>
+      </c>
       <c r="E128" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F128" s="3" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
@@ -3685,41 +3685,555 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 100</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>8809695678363</t>
-        </is>
-      </c>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" s="3" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr"/>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>8809239800458</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye Spot Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>8809239800618</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>8809239802872</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>8809239802896</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>8809239803589</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PRRETI</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PRRETI Honey&amp;Berry Lip Sleeping Mask 15</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>8809738608364</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>8809657114731</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>8809738600221</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>8809738593080</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>8809783325667</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SKIN1004</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>8809738604755</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>8809326334224</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>THE</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml]</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>VT REEDLE SHOT 100</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>8809695678363</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr"/>
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr"/>
-      <c r="D130" s="4" t="inlineStr"/>
-      <c r="E130" s="5" t="n">
-        <v>23759</v>
-      </c>
-      <c r="F130" s="5" t="inlineStr"/>
-      <c r="G130" s="4" t="inlineStr"/>
-      <c r="H130" s="4" t="inlineStr"/>
+      <c r="C151" s="4" t="inlineStr"/>
+      <c r="D151" s="4" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>32689</v>
+      </c>
+      <c r="F151" s="5" t="inlineStr"/>
+      <c r="G151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/Заявка в Корею.xlsx
+++ b/outputs/Заявка в Корею.xlsx
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
       <c r="C151" s="4" t="inlineStr"/>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="5" t="n">
-        <v>32689</v>
+        <v>32639</v>
       </c>
       <c r="F151" s="5" t="inlineStr"/>
       <c r="G151" s="4" t="inlineStr"/>

--- a/outputs/Заявка в Корею.xlsx
+++ b/outputs/Заявка в Корею.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="3" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F64" s="3" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F65" s="3" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="F114" s="3" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>1355</v>
+        <v>1400</v>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F117" s="3" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="F119" s="3" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" s="3" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="F120" s="3" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" s="3" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="F122" s="3" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F123" s="3" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" s="3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="3" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" s="3" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F126" s="3" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F128" s="3" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" s="3" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F130" s="3" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F131" s="3" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="F132" s="3" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="F134" s="3" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F135" s="3" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" s="3" t="n">
-        <v>428</v>
+        <v>400</v>
       </c>
       <c r="F136" s="3" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F137" s="3" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="E138" s="3" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="F138" s="3" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" s="3" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F139" s="3" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F140" s="3" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E144" s="3" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F144" s="3" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
@@ -4229,7 +4229,7 @@
       <c r="C151" s="4" t="inlineStr"/>
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="5" t="n">
-        <v>32639</v>
+        <v>35300</v>
       </c>
       <c r="F151" s="5" t="inlineStr"/>
       <c r="G151" s="4" t="inlineStr"/>
